--- a/public/templates/offer-list-template.xlsx
+++ b/public/templates/offer-list-template.xlsx
@@ -18,6 +18,13 @@
     <sheet name="関連リンク" sheetId="3" r:id="rId4"/>
     <sheet name="変更履歴" sheetId="16" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="extRef1"/>
+    <externalReference r:id="extRef2"/>
+    <externalReference r:id="extRef3"/>
+    <externalReference r:id="extRef4"/>
+    <externalReference r:id="extRef5"/>
+  </externalReferences>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4448,6 +4455,143 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="summary"/>
+      <sheetName val="7月"/>
+      <sheetName val="8月"/>
+      <sheetName val="9月"/>
+      <sheetName val="比較対象1"/>
+      <sheetName val="比較対象2"/>
+      <sheetName val="比較対象3"/>
+      <sheetName val="変更理由"/>
+      <sheetName val="当月MTD"/>
+      <sheetName val="収集値"/>
+      <sheetName val="自動化対象部署"/>
+      <sheetName val="項目一覧"/>
+      <sheetName val="入力規制"/>
+      <sheetName val="小分類表"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="New Format (2)"/>
+      <sheetName val="May.29 (2)"/>
+      <sheetName val="May.29"/>
+      <sheetName val="May.15(2)"/>
+      <sheetName val="May.15"/>
+      <sheetName val="May.1(2)"/>
+      <sheetName val="May.1"/>
+      <sheetName val="Apr.17"/>
+      <sheetName val="Apr.17 (2)"/>
+      <sheetName val="Apr.17 (3)"/>
+      <sheetName val="Apr. 3 (2)"/>
+      <sheetName val="Apr. 3"/>
+      <sheetName val="Mar. 20 (2)"/>
+      <sheetName val="Mar. 20"/>
+      <sheetName val="Mar.6（3）"/>
+      <sheetName val="Mar. 6 (2)"/>
+      <sheetName val="Mar. 6"/>
+      <sheetName val="Feb. 6"/>
+      <sheetName val="Jan. 23"/>
+      <sheetName val="Jan.10"/>
+      <sheetName val="Dec. 26"/>
+      <sheetName val="Dec. 12"/>
+      <sheetName val="Nov.28 (2)"/>
+      <sheetName val="Nov.28"/>
+      <sheetName val="Nov.21"/>
+      <sheetName val="Nov. 14-2　pending中"/>
+      <sheetName val="Nov. 14"/>
+      <sheetName val="Nov.14"/>
+      <sheetName val="Nov.7-2"/>
+      <sheetName val="Nov.7-1"/>
+      <sheetName val="code"/>
+      <sheetName val="New_Format_(2)"/>
+      <sheetName val="May_29_(2)"/>
+      <sheetName val="May_29"/>
+      <sheetName val="May_15(2)"/>
+      <sheetName val="May_15"/>
+      <sheetName val="May_1(2)"/>
+      <sheetName val="May_1"/>
+      <sheetName val="Apr_17"/>
+      <sheetName val="Apr_17_(2)"/>
+      <sheetName val="Apr_17_(3)"/>
+      <sheetName val="Apr__3_(2)"/>
+      <sheetName val="Apr__3"/>
+      <sheetName val="Mar__20_(2)"/>
+      <sheetName val="Mar__20"/>
+      <sheetName val="Mar_6（3）"/>
+      <sheetName val="Mar__6_(2)"/>
+      <sheetName val="Mar__6"/>
+      <sheetName val="Feb__6"/>
+      <sheetName val="Jan__23"/>
+      <sheetName val="Jan_10"/>
+      <sheetName val="Dec__26"/>
+      <sheetName val="Dec__12"/>
+      <sheetName val="Nov_28_(2)"/>
+      <sheetName val="Nov_28"/>
+      <sheetName val="Nov_21"/>
+      <sheetName val="Nov__14-2　pending中"/>
+      <sheetName val="Nov__14"/>
+      <sheetName val="Nov_14"/>
+      <sheetName val="Nov_7-2"/>
+      <sheetName val="Nov_7-1"/>
+    </sheetNames>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="ピボット"/>
+      <sheetName val="案件一覧"/>
+      <sheetName val="リスト"/>
+      <sheetName val="デバイス"/>
+      <sheetName val="案件数確認"/>
+      <sheetName val="Ishida"/>
+      <sheetName val="進捗Ishida"/>
+      <sheetName val="宮崎"/>
+      <sheetName val="年末年始テスト"/>
+      <sheetName val="●案件一覧（FY2012下期）"/>
+      <sheetName val="ピボット (2)"/>
+      <sheetName val="MOP送料無料"/>
+    </sheetNames>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="EX0054_在庫表"/>
+    </sheetNames>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="入力シート"/>
+      <sheetName val="Lookup"/>
+      <sheetName val="最新SKU一覧"/>
+    </sheetNames>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Kaoru Mizuno" id="{08168732-84C0-43B9-9E07-A154D8136744}" userId="S::kaoru_mizuno@oaklawn.co.jp::ae7a9e95-e8ea-4f7a-8989-15242a81c31a" providerId="AD"/>
@@ -4764,7 +4908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" mc:Ignorable="x14ac xr xr2 xr3" ns2:uid="{6D90A1A1-D1D8-48B6-A204-18B087C032CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{6D90A1A1-D1D8-48B6-A204-18B087C032CE}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
@@ -5543,11 +5687,11 @@
       <c r="E20" s="27"/>
       <c r="F20" s="48"/>
       <c r="G20" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F20,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H20" s="50"/>
       <c r="I20" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F20,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J20" s="37">
         <f>ROUNDDOWN(I20*1.1,0)</f>
@@ -5607,11 +5751,11 @@
       <c r="E21" s="27"/>
       <c r="F21" s="48"/>
       <c r="G21" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F21,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H21" s="48"/>
       <c r="I21" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F21,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J21" s="37">
         <f>ROUNDDOWN(I21*1.1,0)</f>
@@ -5671,11 +5815,11 @@
       <c r="E22" s="27"/>
       <c r="F22" s="48"/>
       <c r="G22" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F22,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H22" s="48"/>
       <c r="I22" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F22,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J22" s="37">
         <f>ROUNDDOWN(I22*1.1,0)</f>
@@ -5735,11 +5879,11 @@
       <c r="E23" s="27"/>
       <c r="F23" s="48"/>
       <c r="G23" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F23,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H23" s="48"/>
       <c r="I23" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F23,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J23" s="37">
         <f>ROUNDDOWN(I23*1.1,0)</f>
@@ -5799,11 +5943,11 @@
       <c r="E24" s="27"/>
       <c r="F24" s="48"/>
       <c r="G24" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F24,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H24" s="48"/>
       <c r="I24" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F24,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J24" s="37">
         <f>ROUNDDOWN(I24*1.1,0)</f>
@@ -5863,11 +6007,11 @@
       <c r="E25" s="27"/>
       <c r="F25" s="48"/>
       <c r="G25" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F25,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F25,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J25" s="37">
         <f>ROUNDDOWN(I25*1.1,0)</f>
@@ -5927,11 +6071,11 @@
       <c r="E26" s="27"/>
       <c r="F26" s="48"/>
       <c r="G26" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F26,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H26" s="48"/>
       <c r="I26" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F26,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J26" s="37">
         <f>ROUNDDOWN(I26*1.1,0)</f>
@@ -5991,11 +6135,11 @@
       <c r="E27" s="31"/>
       <c r="F27" s="49"/>
       <c r="G27" s="4" t="str">
-        <v/>
+        <f>IFERROR(VLOOKUP(F27,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
       </c>
       <c r="H27" s="49"/>
       <c r="I27" s="36">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(F27,[5]入力シート!$C:$AH,18,FALSE),0)</f>
       </c>
       <c r="J27" s="37">
         <f>ROUNDDOWN(I27*1.1,0)</f>
@@ -9207,9 +9351,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" ns3:id="rId1"/>
+  <drawing ns3:id="rId2"/>
+  <legacyDrawing ns3:id="rId3"/>
 </worksheet>
 </file>
 

--- a/public/templates/offer-list-template.xlsx
+++ b/public/templates/offer-list-template.xlsx
@@ -18,13 +18,6 @@
     <sheet name="関連リンク" sheetId="3" r:id="rId4"/>
     <sheet name="変更履歴" sheetId="16" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="extRef1"/>
-    <externalReference r:id="extRef2"/>
-    <externalReference r:id="extRef3"/>
-    <externalReference r:id="extRef4"/>
-    <externalReference r:id="extRef5"/>
-  </externalReferences>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4455,143 +4448,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="summary"/>
-      <sheetName val="7月"/>
-      <sheetName val="8月"/>
-      <sheetName val="9月"/>
-      <sheetName val="比較対象1"/>
-      <sheetName val="比較対象2"/>
-      <sheetName val="比較対象3"/>
-      <sheetName val="変更理由"/>
-      <sheetName val="当月MTD"/>
-      <sheetName val="収集値"/>
-      <sheetName val="自動化対象部署"/>
-      <sheetName val="項目一覧"/>
-      <sheetName val="入力規制"/>
-      <sheetName val="小分類表"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="New Format (2)"/>
-      <sheetName val="May.29 (2)"/>
-      <sheetName val="May.29"/>
-      <sheetName val="May.15(2)"/>
-      <sheetName val="May.15"/>
-      <sheetName val="May.1(2)"/>
-      <sheetName val="May.1"/>
-      <sheetName val="Apr.17"/>
-      <sheetName val="Apr.17 (2)"/>
-      <sheetName val="Apr.17 (3)"/>
-      <sheetName val="Apr. 3 (2)"/>
-      <sheetName val="Apr. 3"/>
-      <sheetName val="Mar. 20 (2)"/>
-      <sheetName val="Mar. 20"/>
-      <sheetName val="Mar.6（3）"/>
-      <sheetName val="Mar. 6 (2)"/>
-      <sheetName val="Mar. 6"/>
-      <sheetName val="Feb. 6"/>
-      <sheetName val="Jan. 23"/>
-      <sheetName val="Jan.10"/>
-      <sheetName val="Dec. 26"/>
-      <sheetName val="Dec. 12"/>
-      <sheetName val="Nov.28 (2)"/>
-      <sheetName val="Nov.28"/>
-      <sheetName val="Nov.21"/>
-      <sheetName val="Nov. 14-2　pending中"/>
-      <sheetName val="Nov. 14"/>
-      <sheetName val="Nov.14"/>
-      <sheetName val="Nov.7-2"/>
-      <sheetName val="Nov.7-1"/>
-      <sheetName val="code"/>
-      <sheetName val="New_Format_(2)"/>
-      <sheetName val="May_29_(2)"/>
-      <sheetName val="May_29"/>
-      <sheetName val="May_15(2)"/>
-      <sheetName val="May_15"/>
-      <sheetName val="May_1(2)"/>
-      <sheetName val="May_1"/>
-      <sheetName val="Apr_17"/>
-      <sheetName val="Apr_17_(2)"/>
-      <sheetName val="Apr_17_(3)"/>
-      <sheetName val="Apr__3_(2)"/>
-      <sheetName val="Apr__3"/>
-      <sheetName val="Mar__20_(2)"/>
-      <sheetName val="Mar__20"/>
-      <sheetName val="Mar_6（3）"/>
-      <sheetName val="Mar__6_(2)"/>
-      <sheetName val="Mar__6"/>
-      <sheetName val="Feb__6"/>
-      <sheetName val="Jan__23"/>
-      <sheetName val="Jan_10"/>
-      <sheetName val="Dec__26"/>
-      <sheetName val="Dec__12"/>
-      <sheetName val="Nov_28_(2)"/>
-      <sheetName val="Nov_28"/>
-      <sheetName val="Nov_21"/>
-      <sheetName val="Nov__14-2　pending中"/>
-      <sheetName val="Nov__14"/>
-      <sheetName val="Nov_14"/>
-      <sheetName val="Nov_7-2"/>
-      <sheetName val="Nov_7-1"/>
-    </sheetNames>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="ピボット"/>
-      <sheetName val="案件一覧"/>
-      <sheetName val="リスト"/>
-      <sheetName val="デバイス"/>
-      <sheetName val="案件数確認"/>
-      <sheetName val="Ishida"/>
-      <sheetName val="進捗Ishida"/>
-      <sheetName val="宮崎"/>
-      <sheetName val="年末年始テスト"/>
-      <sheetName val="●案件一覧（FY2012下期）"/>
-      <sheetName val="ピボット (2)"/>
-      <sheetName val="MOP送料無料"/>
-    </sheetNames>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="EX0054_在庫表"/>
-    </sheetNames>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力シート"/>
-      <sheetName val="Lookup"/>
-      <sheetName val="最新SKU一覧"/>
-    </sheetNames>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Kaoru Mizuno" id="{08168732-84C0-43B9-9E07-A154D8136744}" userId="S::kaoru_mizuno@oaklawn.co.jp::ae7a9e95-e8ea-4f7a-8989-15242a81c31a" providerId="AD"/>
@@ -4908,7 +4764,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{6D90A1A1-D1D8-48B6-A204-18B087C032CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" mc:Ignorable="x14ac xr xr2 xr3" ns2:uid="{6D90A1A1-D1D8-48B6-A204-18B087C032CE}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
@@ -5687,11 +5543,11 @@
       <c r="E20" s="27"/>
       <c r="F20" s="48"/>
       <c r="G20" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F20,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H20" s="50"/>
       <c r="I20" s="36">
-        <f>IFERROR(VLOOKUP(F20,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J20" s="37">
         <f>ROUNDDOWN(I20*1.1,0)</f>
@@ -5751,11 +5607,11 @@
       <c r="E21" s="27"/>
       <c r="F21" s="48"/>
       <c r="G21" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F21,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H21" s="48"/>
       <c r="I21" s="36">
-        <f>IFERROR(VLOOKUP(F21,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J21" s="37">
         <f>ROUNDDOWN(I21*1.1,0)</f>
@@ -5815,11 +5671,11 @@
       <c r="E22" s="27"/>
       <c r="F22" s="48"/>
       <c r="G22" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F22,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H22" s="48"/>
       <c r="I22" s="36">
-        <f>IFERROR(VLOOKUP(F22,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J22" s="37">
         <f>ROUNDDOWN(I22*1.1,0)</f>
@@ -5879,11 +5735,11 @@
       <c r="E23" s="27"/>
       <c r="F23" s="48"/>
       <c r="G23" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F23,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H23" s="48"/>
       <c r="I23" s="36">
-        <f>IFERROR(VLOOKUP(F23,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J23" s="37">
         <f>ROUNDDOWN(I23*1.1,0)</f>
@@ -5943,11 +5799,11 @@
       <c r="E24" s="27"/>
       <c r="F24" s="48"/>
       <c r="G24" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F24,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H24" s="48"/>
       <c r="I24" s="36">
-        <f>IFERROR(VLOOKUP(F24,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J24" s="37">
         <f>ROUNDDOWN(I24*1.1,0)</f>
@@ -6007,11 +5863,11 @@
       <c r="E25" s="27"/>
       <c r="F25" s="48"/>
       <c r="G25" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F25,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="36">
-        <f>IFERROR(VLOOKUP(F25,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J25" s="37">
         <f>ROUNDDOWN(I25*1.1,0)</f>
@@ -6071,11 +5927,11 @@
       <c r="E26" s="27"/>
       <c r="F26" s="48"/>
       <c r="G26" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F26,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H26" s="48"/>
       <c r="I26" s="36">
-        <f>IFERROR(VLOOKUP(F26,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J26" s="37">
         <f>ROUNDDOWN(I26*1.1,0)</f>
@@ -6135,11 +5991,11 @@
       <c r="E27" s="31"/>
       <c r="F27" s="49"/>
       <c r="G27" s="4" t="str">
-        <f>IFERROR(VLOOKUP(F27,[4]EX0054_在庫表!$A:$B,2,FALSE),"")</f>
+        <v/>
       </c>
       <c r="H27" s="49"/>
       <c r="I27" s="36">
-        <f>IFERROR(VLOOKUP(F27,[5]入力シート!$C:$AH,18,FALSE),0)</f>
+        <v>0</v>
       </c>
       <c r="J27" s="37">
         <f>ROUNDDOWN(I27*1.1,0)</f>
@@ -9351,9 +9207,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" ns3:id="rId1"/>
-  <drawing ns3:id="rId2"/>
-  <legacyDrawing ns3:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
